--- a/附件包/Vector.xlsx
+++ b/附件包/Vector.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\KratosAI\附件包\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C590B3D1-300A-44EC-B838-C18C1C17A862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C2A51B-2627-4C4C-8412-C43EC707CF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vector 标签" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vector 标签'!$A$1:$D$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="327">
   <si>
     <t>标签名 (Vector.xxx)</t>
   </si>
@@ -139,9 +152,6 @@
     <t>-1</t>
   </si>
   <si>
-    <t>圆半径（lepton）。-1=自动取弹体/单位当前到圆心的 XY 距离。&gt;0 直接使用。每运动帧叠加 CircleRadiusGrow，受 CircleMaxRadius/CircleMinRadius 钳位。</t>
-  </si>
-  <si>
     <t>圆周线速度（lepton/步）。&gt;0 即可独立激活 Circle 模式。每帧叠加加速度，受 CircleMaxSpeed/CircleMinSpeed 钳位。0 时首帧兜底取弹体/单位自身 Speed。与 CircleAnglePerStep 共存时角速度优先——线速度由角速度×半径重算，显式 CircleSpeed 被忽略。</t>
   </si>
   <si>
@@ -164,9 +174,6 @@
   </si>
   <si>
     <t>角速度下限。0=不限。</t>
-  </si>
-  <si>
-    <t>圆心偏移。AllowOriginTilt=no 时直接世界坐标加法（圆心=Origin点+CircleOrigin），无视朝向。AllowOriginTilt=yes 时作为 FLH 偏移跟随转轴旋转（F=沿 facing，L=垂直 facing，H=Z）。</t>
   </si>
   <si>
     <t>int,int</t>
@@ -1495,10 +1502,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Vector.CircleOrigin</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Vector.AllowOriginTilt</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2730,9 +2733,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Vector.Origin.CircleOrigin</t>
-  </si>
-  <si>
     <t>Vector.TargetOffsetNormalOnOrigin</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -3020,35 +3020,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>圆心原点偏移，在基座坐标系上直接加世界坐标偏移量，或随着</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>AllowOriginTilt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>偏移</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
@@ -3099,6 +3070,612 @@
         <charset val="134"/>
       </rPr>
       <t>（新）</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.CircleDynamic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>圆半径（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>lepton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）。每运动帧叠加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CircleRadiusGrow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，受</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CircleMaxRadius/CircleMinRadius </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钳位。</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>yes=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>自动取弹体</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>单位当前到圆心的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> XY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>距离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>同时直接使用当前抛射体的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>高度作为圆心高度</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.Origin.CircleDynamic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.OriginOffsetF</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.OriginOffsetL</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.OriginOffsetH</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.CircleRadiusDynamic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.CircleHeightDynamic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>yes=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>自动取弹体</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>单位当前到圆心的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> XY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>距离做半径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>同时直接使用当前抛射体的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>高度作为圆心高度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。总开关</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>圆心坐标偏移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，取</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>min,max</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>圆心坐标偏移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，取</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>min,max</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>圆心坐标偏移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，取</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>min,max</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.Origin.CircleRadiusDynamic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.Origin.CircleHeightDynamic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.Origin.OriginOffsetF</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.Origin.OriginOffsetL</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.Origin.OriginOffsetH</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大圆圆心坐标偏移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，取</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>min,max</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大圆圆心坐标偏移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，取</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>min,max</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大圆圆心坐标偏移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，取</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>min,max</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>可以显性设</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>no</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>关掉动态大圆的半径部分</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>可以显性设</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>no</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>关掉动态大圆的高度部分</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>可以显性设</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>no</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>关掉动态圆的半径部分</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>可以显性设</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>no</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>关掉动态圆的高度部分</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -3107,7 +3684,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3288,6 +3865,23 @@
       <name val="宋体"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3388,11 +3982,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3419,9 +4010,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3478,12 +4066,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3538,6 +4120,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -3571,17 +4172,23 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3894,399 +4501,399 @@
     <col min="4" max="4" width="144" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+    <row r="2" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="65"/>
-    </row>
-    <row r="3" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="68"/>
+    </row>
+    <row r="3" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="B5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>290</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="35" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="15" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="16" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="57"/>
+    </row>
+    <row r="17" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="51" t="s">
+        <v>244</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="11" t="s">
+      <c r="B18" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C18" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="D18" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="B19" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C19" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="B20" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>244</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="B10" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" s="52" t="s">
-        <v>294</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="B12" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="39" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="16" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="59" t="s">
-        <v>254</v>
-      </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="61"/>
-    </row>
-    <row r="17" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="55" t="s">
-        <v>247</v>
-      </c>
-      <c r="B17" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="56" t="s">
-        <v>230</v>
-      </c>
-      <c r="D17" s="57" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="13" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="50" t="s">
-        <v>281</v>
-      </c>
-      <c r="B19" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="52" t="s">
-        <v>244</v>
-      </c>
-      <c r="D19" s="54" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="B20" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="51" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="50" t="s">
+      <c r="D20" s="47" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B21" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="52" t="s">
-        <v>244</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="50" t="s">
-        <v>290</v>
-      </c>
-      <c r="B22" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="52" t="s">
-        <v>244</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="25" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="26" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="51"/>
-    </row>
-    <row r="28" spans="1:4" s="13" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="51"/>
-      <c r="D28" s="62" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="51"/>
-    </row>
-    <row r="30" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="51"/>
-    </row>
-    <row r="31" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="51"/>
-    </row>
-    <row r="32" spans="1:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" s="39" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" s="39" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" spans="4:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" spans="4:4" s="13" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" spans="4:4" s="44" customFormat="1" x14ac:dyDescent="0.15"/>
+    </row>
+    <row r="24" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="25" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="47"/>
+    </row>
+    <row r="28" spans="1:4" s="12" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="47"/>
+      <c r="D28" s="58" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="47"/>
+    </row>
+    <row r="30" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="47"/>
+    </row>
+    <row r="31" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="47"/>
+    </row>
+    <row r="32" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" s="35" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" s="35" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" spans="4:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" spans="4:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" spans="4:4" s="40" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="132" spans="4:4" x14ac:dyDescent="0.15">
-      <c r="D132" s="29"/>
+      <c r="D132" s="27"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -4311,75 +4918,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
-        <v>251</v>
-      </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="68"/>
+      <c r="A1" s="69" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="71"/>
     </row>
     <row r="2" spans="1:4" ht="24" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="72" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="74"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="71"/>
-    </row>
-    <row r="5" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="B6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>118</v>
+      <c r="D7" s="8" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -4403,405 +5010,405 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="75" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="77"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A7" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="77"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="75" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="77"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="74"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="D18" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A19" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="5" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A24" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A26" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A27" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B27" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="C27" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A29" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="B29" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C29" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A6" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="D29" s="22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A30" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A31" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A7" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="75" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="74"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A11" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A12" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="74"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A14" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" s="11" t="s">
+      <c r="D31" s="23" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A32" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C32" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A22" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A23" s="39" t="s">
-        <v>241</v>
-      </c>
-      <c r="B23" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="46" t="s">
-        <v>286</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="D24" s="58" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A26" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A27" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A28" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A29" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="24" t="s">
+      <c r="D32" s="4" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A30" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A31" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A32" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4817,7 +5424,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1DCE055-F7FB-4EC1-92FA-BFE18C06FC52}">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4827,1227 +5434,1401 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="77"/>
     </row>
     <row r="2" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="79" t="s">
+        <v>306</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="80" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="79" t="s">
+        <v>307</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="80" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="79" t="s">
+        <v>308</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="80" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="48">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A24" s="63" t="s">
+        <v>302</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="63" t="s">
+        <v>309</v>
+      </c>
+      <c r="B25" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="64" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A26" s="63" t="s">
+        <v>310</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="75" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="76"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="77"/>
+    </row>
+    <row r="33" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A38" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="B38" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A39" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="B39" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A40" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="B40" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A41" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="B41" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A42" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="B42" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B43" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="43">
+        <v>0</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="43">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A45" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="B45" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="48">
+        <v>0</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A46" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="B46" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A47" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="B47" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A48" s="42"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="42"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A49" s="42"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+    </row>
+    <row r="50" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A50" s="59" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" s="60"/>
+      <c r="C50" s="60"/>
+      <c r="D50" s="61"/>
+    </row>
+    <row r="51" spans="1:4" ht="24" x14ac:dyDescent="0.2">
+      <c r="A51" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="B51" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A52" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="B52" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A53" s="45" t="s">
+        <v>292</v>
+      </c>
+      <c r="B53" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A54" s="45" t="s">
+        <v>293</v>
+      </c>
+      <c r="B54" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A55" s="42"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="42"/>
+      <c r="D55" s="42"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A56" s="42"/>
+      <c r="B56" s="42"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="42"/>
+    </row>
+    <row r="57" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A57" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="60"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="61"/>
+    </row>
+    <row r="58" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A58" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A59" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="B59" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A60" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="B60" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A61" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="61"/>
+    </row>
+    <row r="62" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A62" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="B62" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A63" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="B63" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="D63" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A64" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="B64" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C64" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="D64" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A65" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="B65" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C65" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A66" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="B66" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A67" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="B67" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C67" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A68" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="B68" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="50" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A69" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="B69" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="11" t="s">
+      <c r="D69" s="50" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A70" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="B70" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" s="48">
+        <v>50</v>
+      </c>
+      <c r="D70" s="50" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A71" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="B71" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="48"/>
+      <c r="D71" s="50" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A72" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="B72" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C72" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="50" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A73" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="B73" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C73" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="50" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A74" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="B74" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="50" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A75" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="B75" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="41" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A76" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="B76" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C76" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" s="41" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A77" s="46" t="s">
+        <v>265</v>
+      </c>
+      <c r="B77" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C77" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="41" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A78" s="42"/>
+      <c r="B78" s="42"/>
+      <c r="C78" s="42"/>
+      <c r="D78" s="42"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A79" s="42"/>
+      <c r="B79" s="42"/>
+      <c r="C79" s="42"/>
+      <c r="D79" s="42"/>
+    </row>
+    <row r="80" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A80" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
+      <c r="D80" s="30"/>
+    </row>
+    <row r="81" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A81" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="B81" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C81" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A82" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="B82" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="D82" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A83" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="B83" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A84" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="B84" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C84" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A85" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B85" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C85" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A86" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="B86" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C86" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="D86" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A87" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="B87" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A88" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="B88" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A89" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="B89" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A90" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="B90" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A91" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="B91" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="44" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A92" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="C92" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A93" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="B93" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="64" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A94" s="83" t="s">
+        <v>315</v>
+      </c>
+      <c r="B94" s="81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="81" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="84" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A95" s="83" t="s">
+        <v>316</v>
+      </c>
+      <c r="B95" s="81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="81" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="84" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A96" s="85" t="s">
+        <v>317</v>
+      </c>
+      <c r="B96" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="C96" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96" s="86" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A97" s="85" t="s">
+        <v>318</v>
+      </c>
+      <c r="B97" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="86" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A98" s="85" t="s">
+        <v>319</v>
+      </c>
+      <c r="B98" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="C98" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98" s="86" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A101" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="B101" s="31"/>
+      <c r="C101" s="31"/>
+      <c r="D101" s="32"/>
+    </row>
+    <row r="102" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A102" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="B102" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A103" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="B103" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C103" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A104" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="B104" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A105" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="B105" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C105" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A106" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="B106" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C106" s="43">
+        <v>0</v>
+      </c>
+      <c r="D106" s="44" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A107" s="45" t="s">
+        <v>270</v>
+      </c>
+      <c r="B107" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C107" s="43">
+        <v>0</v>
+      </c>
+      <c r="D107" s="44" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A108" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="B108" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C108" s="43">
+        <v>0</v>
+      </c>
+      <c r="D108" s="44" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A109" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="B109" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="D109" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A110" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="B110" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C110" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B9" s="11" t="s">
+      <c r="D110" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A111" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="B111" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C111" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A20" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" s="52">
-        <v>0</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="74"/>
-    </row>
-    <row r="24" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A27" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A28" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A30" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A32" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A33" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A34" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="1">
-        <v>0</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A36" s="50" t="s">
-        <v>258</v>
-      </c>
-      <c r="B36" s="52" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" s="52">
-        <v>0</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A37" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="B37" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="52" t="s">
-        <v>244</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A38" s="50" t="s">
-        <v>295</v>
-      </c>
-      <c r="B38" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A41" s="76" t="s">
-        <v>115</v>
-      </c>
-      <c r="B41" s="77"/>
-      <c r="C41" s="77"/>
-      <c r="D41" s="78"/>
-    </row>
-    <row r="42" spans="1:4" ht="24" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A44" s="49" t="s">
-        <v>296</v>
-      </c>
-      <c r="B44" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A45" s="49" t="s">
-        <v>297</v>
-      </c>
-      <c r="B45" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="C45" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A48" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="77"/>
-      <c r="C48" s="77"/>
-      <c r="D48" s="78"/>
-    </row>
-    <row r="49" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A50" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A51" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="B51" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A52" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="36"/>
-    </row>
-    <row r="53" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A53" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="B53" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A54" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B54" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A55" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="B55" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A56" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B56" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A57" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B57" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A58" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="B58" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A59" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="B59" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" s="25" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A60" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B60" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A61" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="B61" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C61" s="23">
-        <v>50</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A62" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="B62" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="23"/>
-      <c r="D62" s="25" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A63" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B63" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C63" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D63" s="25" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A64" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="B64" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C64" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A65" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="B65" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C65" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A66" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="B66" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D66" s="45" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A67" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="B67" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C67" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D67" s="45" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A68" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="B68" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C68" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D68" s="45" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A71" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="B71" s="31"/>
-      <c r="C71" s="31"/>
-      <c r="D71" s="32"/>
-    </row>
-    <row r="72" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A72" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A73" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A74" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D75" s="17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D76" s="17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A79" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A80" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A81" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A82" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A83" s="49" t="s">
-        <v>285</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A84" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D84" s="17" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A88" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="B88" s="33"/>
-      <c r="C88" s="33"/>
-      <c r="D88" s="34"/>
-    </row>
-    <row r="89" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A91" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A92" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A93" s="49" t="s">
-        <v>272</v>
-      </c>
-      <c r="B93" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="C93" s="47">
-        <v>0</v>
-      </c>
-      <c r="D93" s="48" t="s">
+      <c r="D111" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A112" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="B112" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="C112" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="D112" s="39" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A113" s="37" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A94" s="49" t="s">
-        <v>273</v>
-      </c>
-      <c r="B94" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="C94" s="47">
-        <v>0</v>
-      </c>
-      <c r="D94" s="48" t="s">
+      <c r="B113" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="C113" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="D113" s="39" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A95" s="49" t="s">
-        <v>274</v>
-      </c>
-      <c r="B95" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="C95" s="47">
-        <v>0</v>
-      </c>
-      <c r="D95" s="48" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A96" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B96" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A97" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A98" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A99" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="B99" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="C99" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="D99" s="43" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A100" s="41" t="s">
-        <v>303</v>
-      </c>
-      <c r="B100" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="C100" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="D100" s="43" t="s">
-        <v>304</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A48:D48"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
